--- a/Resultados_Consolidados_PRP.xlsx
+++ b/Resultados_Consolidados_PRP.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="199">
   <si>
     <t>Instancia</t>
   </si>
@@ -42,7 +42,13 @@
     <t>Gap_Percentual</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>ABS1_50_6.dat</t>
+  </si>
+  <si>
+    <t>✔️ OK</t>
   </si>
   <si>
     <t>ABS2_50_6.dat</t>
@@ -967,10 +973,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:F193"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -986,10 +992,13 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="n">
         <v>50</v>
@@ -1003,10 +1012,13 @@
       <c r="E2" t="n">
         <v>10.53</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="n">
         <v>50</v>
@@ -1020,10 +1032,13 @@
       <c r="E3" t="n">
         <v>11.31</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="n">
         <v>50</v>
@@ -1037,10 +1052,13 @@
       <c r="E4" t="n">
         <v>12.98</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="n">
         <v>50</v>
@@ -1054,10 +1072,13 @@
       <c r="E5" t="n">
         <v>7.9</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="n">
         <v>50</v>
@@ -1071,10 +1092,13 @@
       <c r="E6" t="n">
         <v>8.25</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B7" t="n">
         <v>50</v>
@@ -1088,10 +1112,13 @@
       <c r="E7" t="n">
         <v>9.12</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" t="n">
         <v>50</v>
@@ -1105,10 +1132,13 @@
       <c r="E8" t="n">
         <v>9.55</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B9" t="n">
         <v>50</v>
@@ -1122,10 +1152,13 @@
       <c r="E9" t="n">
         <v>10.68</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B10" t="n">
         <v>50</v>
@@ -1139,10 +1172,13 @@
       <c r="E10" t="n">
         <v>12.77</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B11" t="n">
         <v>50</v>
@@ -1156,10 +1192,13 @@
       <c r="E11" t="n">
         <v>6.28</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B12" t="n">
         <v>50</v>
@@ -1173,10 +1212,13 @@
       <c r="E12" t="n">
         <v>6.68</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B13" t="n">
         <v>50</v>
@@ -1190,10 +1232,13 @@
       <c r="E13" t="n">
         <v>7.65</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B14" t="n">
         <v>50</v>
@@ -1207,10 +1252,13 @@
       <c r="E14" t="n">
         <v>13.95</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B15" t="n">
         <v>50</v>
@@ -1224,10 +1272,13 @@
       <c r="E15" t="n">
         <v>15.27</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B16" t="n">
         <v>50</v>
@@ -1241,10 +1292,13 @@
       <c r="E16" t="n">
         <v>17.86</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B17" t="n">
         <v>50</v>
@@ -1258,10 +1312,13 @@
       <c r="E17" t="n">
         <v>9.03</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B18" t="n">
         <v>50</v>
@@ -1275,10 +1332,13 @@
       <c r="E18" t="n">
         <v>9.64</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B19" t="n">
         <v>50</v>
@@ -1292,10 +1352,13 @@
       <c r="E19" t="n">
         <v>11.4</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B20" t="n">
         <v>50</v>
@@ -1309,10 +1372,13 @@
       <c r="E20" t="n">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B21" t="n">
         <v>50</v>
@@ -1326,10 +1392,13 @@
       <c r="E21" t="n">
         <v>14.3</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B22" t="n">
         <v>50</v>
@@ -1343,10 +1412,13 @@
       <c r="E22" t="n">
         <v>18.03</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B23" t="n">
         <v>50</v>
@@ -1360,10 +1432,13 @@
       <c r="E23" t="n">
         <v>7.83</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B24" t="n">
         <v>50</v>
@@ -1377,10 +1452,13 @@
       <c r="E24" t="n">
         <v>8.61</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B25" t="n">
         <v>50</v>
@@ -1394,10 +1472,13 @@
       <c r="E25" t="n">
         <v>10.43</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B26" t="n">
         <v>50</v>
@@ -1411,10 +1492,13 @@
       <c r="E26" t="n">
         <v>1.95</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B27" t="n">
         <v>50</v>
@@ -1428,10 +1512,13 @@
       <c r="E27" t="n">
         <v>2.07</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B28" t="n">
         <v>50</v>
@@ -1445,10 +1532,13 @@
       <c r="E28" t="n">
         <v>2.36</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B29" t="n">
         <v>50</v>
@@ -1462,10 +1552,13 @@
       <c r="E29" t="n">
         <v>2.14</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B30" t="n">
         <v>50</v>
@@ -1479,10 +1572,13 @@
       <c r="E30" t="n">
         <v>2.19</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B31" t="n">
         <v>50</v>
@@ -1496,10 +1592,13 @@
       <c r="E31" t="n">
         <v>2.31</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B32" t="n">
         <v>50</v>
@@ -1513,10 +1612,13 @@
       <c r="E32" t="n">
         <v>2.44</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="F32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B33" t="n">
         <v>50</v>
@@ -1530,10 +1632,13 @@
       <c r="E33" t="n">
         <v>2.58</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="F33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B34" t="n">
         <v>50</v>
@@ -1547,10 +1652,13 @@
       <c r="E34" t="n">
         <v>2.85</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="F34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B35" t="n">
         <v>50</v>
@@ -1564,10 +1672,13 @@
       <c r="E35" t="n">
         <v>2.07</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="F35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B36" t="n">
         <v>50</v>
@@ -1581,10 +1692,13 @@
       <c r="E36" t="n">
         <v>2.12</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="F36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B37" t="n">
         <v>50</v>
@@ -1598,10 +1712,13 @@
       <c r="E37" t="n">
         <v>2.21</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="F37" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B38" t="n">
         <v>50</v>
@@ -1615,10 +1732,13 @@
       <c r="E38" t="n">
         <v>2.71</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="F38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B39" t="n">
         <v>50</v>
@@ -1632,10 +1752,13 @@
       <c r="E39" t="n">
         <v>3.01</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="F39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B40" t="n">
         <v>50</v>
@@ -1649,10 +1772,13 @@
       <c r="E40" t="n">
         <v>3.39</v>
       </c>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="F40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B41" t="n">
         <v>50</v>
@@ -1666,10 +1792,13 @@
       <c r="E41" t="n">
         <v>2.34</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="F41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B42" t="n">
         <v>50</v>
@@ -1683,10 +1812,13 @@
       <c r="E42" t="n">
         <v>2.43</v>
       </c>
-    </row>
-    <row r="43" spans="1:5">
+      <c r="F42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B43" t="n">
         <v>50</v>
@@ -1700,10 +1832,13 @@
       <c r="E43" t="n">
         <v>2.66</v>
       </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="F43" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B44" t="n">
         <v>50</v>
@@ -1717,10 +1852,13 @@
       <c r="E44" t="n">
         <v>3.0</v>
       </c>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="F44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B45" t="n">
         <v>50</v>
@@ -1734,10 +1872,13 @@
       <c r="E45" t="n">
         <v>3.23</v>
       </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="F45" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B46" t="n">
         <v>50</v>
@@ -1751,10 +1892,13 @@
       <c r="E46" t="n">
         <v>3.82</v>
       </c>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="F46" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B47" t="n">
         <v>50</v>
@@ -1768,10 +1912,13 @@
       <c r="E47" t="n">
         <v>2.34</v>
       </c>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="F47" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B48" t="n">
         <v>50</v>
@@ -1785,10 +1932,13 @@
       <c r="E48" t="n">
         <v>2.43</v>
       </c>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="F48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B49" t="n">
         <v>50</v>
@@ -1802,10 +1952,13 @@
       <c r="E49" t="n">
         <v>2.63</v>
       </c>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="F49" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B50" t="n">
         <v>50</v>
@@ -1819,10 +1972,13 @@
       <c r="E50" t="n">
         <v>19.27</v>
       </c>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="F50" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B51" t="n">
         <v>50</v>
@@ -1836,10 +1992,13 @@
       <c r="E51" t="n">
         <v>21.91</v>
       </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="F51" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B52" t="n">
         <v>50</v>
@@ -1853,10 +2012,13 @@
       <c r="E52" t="n">
         <v>26.81</v>
       </c>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="F52" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B53" t="n">
         <v>50</v>
@@ -1870,10 +2032,13 @@
       <c r="E53" t="n">
         <v>8.44</v>
       </c>
-    </row>
-    <row r="54" spans="1:5">
+      <c r="F53" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B54" t="n">
         <v>50</v>
@@ -1887,10 +2052,13 @@
       <c r="E54" t="n">
         <v>13.73</v>
       </c>
-    </row>
-    <row r="55" spans="1:5">
+      <c r="F54" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B55" t="n">
         <v>50</v>
@@ -1904,10 +2072,13 @@
       <c r="E55" t="n">
         <v>17.67</v>
       </c>
-    </row>
-    <row r="56" spans="1:5">
+      <c r="F55" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B56" t="n">
         <v>50</v>
@@ -1921,10 +2092,13 @@
       <c r="E56" t="n">
         <v>19.62</v>
       </c>
-    </row>
-    <row r="57" spans="1:5">
+      <c r="F56" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B57" t="n">
         <v>50</v>
@@ -1938,10 +2112,13 @@
       <c r="E57" t="n">
         <v>23.38</v>
       </c>
-    </row>
-    <row r="58" spans="1:5">
+      <c r="F57" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B58" t="n">
         <v>50</v>
@@ -1955,10 +2132,13 @@
       <c r="E58" t="n">
         <v>29.25</v>
       </c>
-    </row>
-    <row r="59" spans="1:5">
+      <c r="F58" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B59" t="n">
         <v>50</v>
@@ -1972,10 +2152,13 @@
       <c r="E59" t="n">
         <v>12.08</v>
       </c>
-    </row>
-    <row r="60" spans="1:5">
+      <c r="F59" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B60" t="n">
         <v>50</v>
@@ -1989,10 +2172,13 @@
       <c r="E60" t="n">
         <v>14.15</v>
       </c>
-    </row>
-    <row r="61" spans="1:5">
+      <c r="F60" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B61" t="n">
         <v>50</v>
@@ -2006,10 +2192,13 @@
       <c r="E61" t="n">
         <v>17.76</v>
       </c>
-    </row>
-    <row r="62" spans="1:5">
+      <c r="F61" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B62" t="n">
         <v>50</v>
@@ -2023,10 +2212,13 @@
       <c r="E62" t="n">
         <v>25.24</v>
       </c>
-    </row>
-    <row r="63" spans="1:5">
+      <c r="F62" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B63" t="n">
         <v>50</v>
@@ -2040,10 +2232,13 @@
       <c r="E63" t="n">
         <v>29.75</v>
       </c>
-    </row>
-    <row r="64" spans="1:5">
+      <c r="F63" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B64" t="n">
         <v>50</v>
@@ -2057,10 +2252,13 @@
       <c r="E64" t="n">
         <v>36.01</v>
       </c>
-    </row>
-    <row r="65" spans="1:5">
+      <c r="F64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B65" t="n">
         <v>50</v>
@@ -2074,10 +2272,13 @@
       <c r="E65" t="n">
         <v>17.05</v>
       </c>
-    </row>
-    <row r="66" spans="1:5">
+      <c r="F65" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B66" t="n">
         <v>50</v>
@@ -2091,10 +2292,13 @@
       <c r="E66" t="n">
         <v>19.64</v>
       </c>
-    </row>
-    <row r="67" spans="1:5">
+      <c r="F66" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B67" t="n">
         <v>50</v>
@@ -2108,10 +2312,13 @@
       <c r="E67" t="n">
         <v>25.04</v>
       </c>
-    </row>
-    <row r="68" spans="1:5">
+      <c r="F67" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B68" t="n">
         <v>50</v>
@@ -2125,10 +2332,13 @@
       <c r="E68" t="n">
         <v>27.47</v>
       </c>
-    </row>
-    <row r="69" spans="1:5">
+      <c r="F68" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B69" t="n">
         <v>50</v>
@@ -2142,10 +2352,13 @@
       <c r="E69" t="n">
         <v>31.19</v>
       </c>
-    </row>
-    <row r="70" spans="1:5">
+      <c r="F69" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B70" t="n">
         <v>50</v>
@@ -2159,10 +2372,13 @@
       <c r="E70" t="n">
         <v>39.76</v>
       </c>
-    </row>
-    <row r="71" spans="1:5">
+      <c r="F70" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B71" t="n">
         <v>50</v>
@@ -2176,10 +2392,13 @@
       <c r="E71" t="n">
         <v>18.57</v>
       </c>
-    </row>
-    <row r="72" spans="1:5">
+      <c r="F71" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B72" t="n">
         <v>50</v>
@@ -2193,10 +2412,13 @@
       <c r="E72" t="n">
         <v>21.12</v>
       </c>
-    </row>
-    <row r="73" spans="1:5">
+      <c r="F72" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B73" t="n">
         <v>50</v>
@@ -2210,10 +2432,13 @@
       <c r="E73" t="n">
         <v>26.78</v>
       </c>
-    </row>
-    <row r="74" spans="1:5">
+      <c r="F73" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B74" t="n">
         <v>50</v>
@@ -2227,10 +2452,13 @@
       <c r="E74" t="n">
         <v>10.43</v>
       </c>
-    </row>
-    <row r="75" spans="1:5">
+      <c r="F74" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B75" t="n">
         <v>50</v>
@@ -2244,10 +2472,13 @@
       <c r="E75" t="n">
         <v>11.62</v>
       </c>
-    </row>
-    <row r="76" spans="1:5">
+      <c r="F75" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B76" t="n">
         <v>50</v>
@@ -2261,10 +2492,13 @@
       <c r="E76" t="n">
         <v>14.06</v>
       </c>
-    </row>
-    <row r="77" spans="1:5">
+      <c r="F76" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B77" t="n">
         <v>50</v>
@@ -2278,10 +2512,13 @@
       <c r="E77" t="n">
         <v>6.96</v>
       </c>
-    </row>
-    <row r="78" spans="1:5">
+      <c r="F77" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B78" t="n">
         <v>50</v>
@@ -2295,10 +2532,13 @@
       <c r="E78" t="n">
         <v>7.62</v>
       </c>
-    </row>
-    <row r="79" spans="1:5">
+      <c r="F78" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B79" t="n">
         <v>50</v>
@@ -2312,10 +2552,13 @@
       <c r="E79" t="n">
         <v>8.31</v>
       </c>
-    </row>
-    <row r="80" spans="1:5">
+      <c r="F79" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B80" t="n">
         <v>50</v>
@@ -2329,10 +2572,13 @@
       <c r="E80" t="n">
         <v>14.77</v>
       </c>
-    </row>
-    <row r="81" spans="1:5">
+      <c r="F80" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B81" t="n">
         <v>50</v>
@@ -2346,10 +2592,13 @@
       <c r="E81" t="n">
         <v>16.65</v>
       </c>
-    </row>
-    <row r="82" spans="1:5">
+      <c r="F81" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B82" t="n">
         <v>50</v>
@@ -2363,10 +2612,13 @@
       <c r="E82" t="n">
         <v>20.61</v>
       </c>
-    </row>
-    <row r="83" spans="1:5">
+      <c r="F82" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B83" t="n">
         <v>50</v>
@@ -2380,10 +2632,13 @@
       <c r="E83" t="n">
         <v>9.38</v>
       </c>
-    </row>
-    <row r="84" spans="1:5">
+      <c r="F83" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B84" t="n">
         <v>50</v>
@@ -2397,10 +2652,13 @@
       <c r="E84" t="n">
         <v>10.22</v>
       </c>
-    </row>
-    <row r="85" spans="1:5">
+      <c r="F84" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B85" t="n">
         <v>50</v>
@@ -2414,10 +2672,13 @@
       <c r="E85" t="n">
         <v>12.25</v>
       </c>
-    </row>
-    <row r="86" spans="1:5">
+      <c r="F85" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B86" t="n">
         <v>50</v>
@@ -2431,10 +2692,13 @@
       <c r="E86" t="n">
         <v>2.6</v>
       </c>
-    </row>
-    <row r="87" spans="1:5">
+      <c r="F86" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B87" t="n">
         <v>50</v>
@@ -2448,10 +2712,13 @@
       <c r="E87" t="n">
         <v>2.7</v>
       </c>
-    </row>
-    <row r="88" spans="1:5">
+      <c r="F87" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B88" t="n">
         <v>50</v>
@@ -2465,10 +2732,13 @@
       <c r="E88" t="n">
         <v>2.97</v>
       </c>
-    </row>
-    <row r="89" spans="1:5">
+      <c r="F88" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B89" t="n">
         <v>50</v>
@@ -2482,10 +2752,13 @@
       <c r="E89" t="n">
         <v>2.07</v>
       </c>
-    </row>
-    <row r="90" spans="1:5">
+      <c r="F89" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B90" t="n">
         <v>50</v>
@@ -2499,10 +2772,13 @@
       <c r="E90" t="n">
         <v>2.14</v>
       </c>
-    </row>
-    <row r="91" spans="1:5">
+      <c r="F90" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B91" t="n">
         <v>50</v>
@@ -2516,10 +2792,13 @@
       <c r="E91" t="n">
         <v>2.22</v>
       </c>
-    </row>
-    <row r="92" spans="1:5">
+      <c r="F91" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B92" t="n">
         <v>50</v>
@@ -2533,10 +2812,13 @@
       <c r="E92" t="n">
         <v>3.18</v>
       </c>
-    </row>
-    <row r="93" spans="1:5">
+      <c r="F92" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B93" t="n">
         <v>50</v>
@@ -2550,10 +2832,13 @@
       <c r="E93" t="n">
         <v>3.48</v>
       </c>
-    </row>
-    <row r="94" spans="1:5">
+      <c r="F93" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B94" t="n">
         <v>50</v>
@@ -2567,10 +2852,13 @@
       <c r="E94" t="n">
         <v>4.01</v>
       </c>
-    </row>
-    <row r="95" spans="1:5">
+      <c r="F94" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B95" t="n">
         <v>50</v>
@@ -2584,10 +2872,13 @@
       <c r="E95" t="n">
         <v>2.4</v>
       </c>
-    </row>
-    <row r="96" spans="1:5">
+      <c r="F95" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B96" t="n">
         <v>50</v>
@@ -2601,10 +2892,13 @@
       <c r="E96" t="n">
         <v>2.48</v>
       </c>
-    </row>
-    <row r="97" spans="1:5">
+      <c r="F96" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B97" t="n">
         <v>50</v>
@@ -2618,10 +2912,13 @@
       <c r="E97" t="n">
         <v>2.69</v>
       </c>
-    </row>
-    <row r="98" spans="1:5">
+      <c r="F97" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B98" t="n">
         <v>100</v>
@@ -2635,10 +2932,13 @@
       <c r="E98" t="n">
         <v>9.17</v>
       </c>
-    </row>
-    <row r="99" spans="1:5">
+      <c r="F98" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B99" t="n">
         <v>100</v>
@@ -2652,10 +2952,13 @@
       <c r="E99" t="n">
         <v>10.14</v>
       </c>
-    </row>
-    <row r="100" spans="1:5">
+      <c r="F99" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B100" t="n">
         <v>100</v>
@@ -2669,10 +2972,13 @@
       <c r="E100" t="n">
         <v>12.09</v>
       </c>
-    </row>
-    <row r="101" spans="1:5">
+      <c r="F100" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B101" t="n">
         <v>100</v>
@@ -2686,10 +2992,13 @@
       <c r="E101" t="n">
         <v>6.91</v>
       </c>
-    </row>
-    <row r="102" spans="1:5">
+      <c r="F101" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B102" t="n">
         <v>100</v>
@@ -2703,10 +3012,13 @@
       <c r="E102" t="n">
         <v>7.36</v>
       </c>
-    </row>
-    <row r="103" spans="1:5">
+      <c r="F102" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B103" t="n">
         <v>100</v>
@@ -2720,10 +3032,13 @@
       <c r="E103" t="n">
         <v>8.46</v>
       </c>
-    </row>
-    <row r="104" spans="1:5">
+      <c r="F103" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B104" t="n">
         <v>100</v>
@@ -2737,10 +3052,13 @@
       <c r="E104" t="n">
         <v>8.96</v>
       </c>
-    </row>
-    <row r="105" spans="1:5">
+      <c r="F104" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B105" t="n">
         <v>100</v>
@@ -2754,10 +3072,13 @@
       <c r="E105" t="n">
         <v>10.15</v>
       </c>
-    </row>
-    <row r="106" spans="1:5">
+      <c r="F105" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B106" t="n">
         <v>100</v>
@@ -2771,10 +3092,13 @@
       <c r="E106" t="n">
         <v>12.97</v>
       </c>
-    </row>
-    <row r="107" spans="1:5">
+      <c r="F106" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B107" t="n">
         <v>100</v>
@@ -2788,10 +3112,13 @@
       <c r="E107" t="n">
         <v>4.66</v>
       </c>
-    </row>
-    <row r="108" spans="1:5">
+      <c r="F107" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B108" t="n">
         <v>100</v>
@@ -2805,10 +3132,13 @@
       <c r="E108" t="n">
         <v>5.25</v>
       </c>
-    </row>
-    <row r="109" spans="1:5">
+      <c r="F108" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B109" t="n">
         <v>100</v>
@@ -2822,10 +3152,13 @@
       <c r="E109" t="n">
         <v>6.39</v>
       </c>
-    </row>
-    <row r="110" spans="1:5">
+      <c r="F109" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B110" t="n">
         <v>100</v>
@@ -2839,10 +3172,13 @@
       <c r="E110" t="n">
         <v>13.48</v>
       </c>
-    </row>
-    <row r="111" spans="1:5">
+      <c r="F110" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B111" t="n">
         <v>100</v>
@@ -2856,10 +3192,13 @@
       <c r="E111" t="n">
         <v>14.95</v>
       </c>
-    </row>
-    <row r="112" spans="1:5">
+      <c r="F111" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B112" t="n">
         <v>100</v>
@@ -2873,10 +3212,13 @@
       <c r="E112" t="n">
         <v>18.26</v>
       </c>
-    </row>
-    <row r="113" spans="1:5">
+      <c r="F112" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B113" t="n">
         <v>100</v>
@@ -2890,10 +3232,13 @@
       <c r="E113" t="n">
         <v>8.57</v>
       </c>
-    </row>
-    <row r="114" spans="1:5">
+      <c r="F113" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B114" t="n">
         <v>100</v>
@@ -2907,10 +3252,13 @@
       <c r="E114" t="n">
         <v>9.67</v>
       </c>
-    </row>
-    <row r="115" spans="1:5">
+      <c r="F114" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B115" t="n">
         <v>100</v>
@@ -2924,10 +3272,13 @@
       <c r="E115" t="n">
         <v>11.43</v>
       </c>
-    </row>
-    <row r="116" spans="1:5">
+      <c r="F115" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B116" t="n">
         <v>100</v>
@@ -2941,10 +3292,13 @@
       <c r="E116" t="n">
         <v>12.26</v>
       </c>
-    </row>
-    <row r="117" spans="1:5">
+      <c r="F116" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B117" t="n">
         <v>100</v>
@@ -2958,10 +3312,13 @@
       <c r="E117" t="n">
         <v>14.35</v>
       </c>
-    </row>
-    <row r="118" spans="1:5">
+      <c r="F117" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B118" t="n">
         <v>100</v>
@@ -2975,10 +3332,13 @@
       <c r="E118" t="n">
         <v>18.96</v>
       </c>
-    </row>
-    <row r="119" spans="1:5">
+      <c r="F118" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B119" t="n">
         <v>100</v>
@@ -2992,10 +3352,13 @@
       <c r="E119" t="n">
         <v>6.31</v>
       </c>
-    </row>
-    <row r="120" spans="1:5">
+      <c r="F119" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B120" t="n">
         <v>100</v>
@@ -3009,10 +3372,13 @@
       <c r="E120" t="n">
         <v>7.34</v>
       </c>
-    </row>
-    <row r="121" spans="1:5">
+      <c r="F120" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B121" t="n">
         <v>100</v>
@@ -3026,10 +3392,13 @@
       <c r="E121" t="n">
         <v>9.51</v>
       </c>
-    </row>
-    <row r="122" spans="1:5">
+      <c r="F121" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B122" t="n">
         <v>100</v>
@@ -3043,10 +3412,13 @@
       <c r="E122" t="n">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="123" spans="1:5">
+      <c r="F122" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B123" t="n">
         <v>100</v>
@@ -3060,10 +3432,13 @@
       <c r="E123" t="n">
         <v>2.04</v>
       </c>
-    </row>
-    <row r="124" spans="1:5">
+      <c r="F123" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B124" t="n">
         <v>100</v>
@@ -3077,10 +3452,13 @@
       <c r="E124" t="n">
         <v>2.39</v>
       </c>
-    </row>
-    <row r="125" spans="1:5">
+      <c r="F124" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B125" t="n">
         <v>100</v>
@@ -3094,10 +3472,13 @@
       <c r="E125" t="n">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="126" spans="1:5">
+      <c r="F125" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B126" t="n">
         <v>100</v>
@@ -3111,10 +3492,13 @@
       <c r="E126" t="n">
         <v>1.77</v>
       </c>
-    </row>
-    <row r="127" spans="1:5">
+      <c r="F126" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B127" t="n">
         <v>100</v>
@@ -3128,10 +3512,13 @@
       <c r="E127" t="n">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="128" spans="1:5">
+      <c r="F127" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B128" t="n">
         <v>100</v>
@@ -3145,10 +3532,13 @@
       <c r="E128" t="n">
         <v>1.94</v>
       </c>
-    </row>
-    <row r="129" spans="1:5">
+      <c r="F128" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B129" t="n">
         <v>100</v>
@@ -3162,10 +3552,13 @@
       <c r="E129" t="n">
         <v>2.11</v>
       </c>
-    </row>
-    <row r="130" spans="1:5">
+      <c r="F129" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B130" t="n">
         <v>100</v>
@@ -3179,10 +3572,13 @@
       <c r="E130" t="n">
         <v>2.45</v>
       </c>
-    </row>
-    <row r="131" spans="1:5">
+      <c r="F130" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B131" t="n">
         <v>100</v>
@@ -3196,10 +3592,13 @@
       <c r="E131" t="n">
         <v>1.24</v>
       </c>
-    </row>
-    <row r="132" spans="1:5">
+      <c r="F131" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B132" t="n">
         <v>100</v>
@@ -3213,10 +3612,13 @@
       <c r="E132" t="n">
         <v>1.29</v>
       </c>
-    </row>
-    <row r="133" spans="1:5">
+      <c r="F132" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B133" t="n">
         <v>100</v>
@@ -3230,10 +3632,13 @@
       <c r="E133" t="n">
         <v>1.42</v>
       </c>
-    </row>
-    <row r="134" spans="1:5">
+      <c r="F133" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B134" t="n">
         <v>100</v>
@@ -3247,10 +3652,13 @@
       <c r="E134" t="n">
         <v>2.63</v>
       </c>
-    </row>
-    <row r="135" spans="1:5">
+      <c r="F134" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B135" t="n">
         <v>100</v>
@@ -3264,10 +3672,13 @@
       <c r="E135" t="n">
         <v>2.96</v>
       </c>
-    </row>
-    <row r="136" spans="1:5">
+      <c r="F135" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B136" t="n">
         <v>100</v>
@@ -3281,10 +3692,13 @@
       <c r="E136" t="n">
         <v>3.58</v>
       </c>
-    </row>
-    <row r="137" spans="1:5">
+      <c r="F136" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B137" t="n">
         <v>100</v>
@@ -3298,10 +3712,13 @@
       <c r="E137" t="n">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="138" spans="1:5">
+      <c r="F137" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B138" t="n">
         <v>100</v>
@@ -3315,10 +3732,13 @@
       <c r="E138" t="n">
         <v>2.05</v>
       </c>
-    </row>
-    <row r="139" spans="1:5">
+      <c r="F138" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B139" t="n">
         <v>100</v>
@@ -3332,10 +3752,13 @@
       <c r="E139" t="n">
         <v>2.31</v>
       </c>
-    </row>
-    <row r="140" spans="1:5">
+      <c r="F139" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B140" t="n">
         <v>100</v>
@@ -3349,10 +3772,13 @@
       <c r="E140" t="n">
         <v>2.51</v>
       </c>
-    </row>
-    <row r="141" spans="1:5">
+      <c r="F140" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B141" t="n">
         <v>100</v>
@@ -3366,10 +3792,13 @@
       <c r="E141" t="n">
         <v>2.9</v>
       </c>
-    </row>
-    <row r="142" spans="1:5">
+      <c r="F141" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B142" t="n">
         <v>100</v>
@@ -3383,10 +3812,13 @@
       <c r="E142" t="n">
         <v>3.63</v>
       </c>
-    </row>
-    <row r="143" spans="1:5">
+      <c r="F142" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B143" t="n">
         <v>100</v>
@@ -3400,10 +3832,13 @@
       <c r="E143" t="n">
         <v>1.49</v>
       </c>
-    </row>
-    <row r="144" spans="1:5">
+      <c r="F143" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B144" t="n">
         <v>100</v>
@@ -3417,10 +3852,13 @@
       <c r="E144" t="n">
         <v>1.62</v>
       </c>
-    </row>
-    <row r="145" spans="1:5">
+      <c r="F144" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B145" t="n">
         <v>100</v>
@@ -3434,10 +3872,13 @@
       <c r="E145" t="n">
         <v>1.89</v>
       </c>
-    </row>
-    <row r="146" spans="1:5">
+      <c r="F145" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B146" t="n">
         <v>100</v>
@@ -3451,10 +3892,13 @@
       <c r="E146" t="n">
         <v>20.55</v>
       </c>
-    </row>
-    <row r="147" spans="1:5">
+      <c r="F146" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B147" t="n">
         <v>100</v>
@@ -3468,10 +3912,13 @@
       <c r="E147" t="n">
         <v>23.71</v>
       </c>
-    </row>
-    <row r="148" spans="1:5">
+      <c r="F147" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B148" t="n">
         <v>100</v>
@@ -3485,10 +3932,13 @@
       <c r="E148" t="n">
         <v>29.54</v>
       </c>
-    </row>
-    <row r="149" spans="1:5">
+      <c r="F148" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B149" t="n">
         <v>100</v>
@@ -3502,10 +3952,13 @@
       <c r="E149" t="n">
         <v>11.77</v>
       </c>
-    </row>
-    <row r="150" spans="1:5">
+      <c r="F149" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B150" t="n">
         <v>100</v>
@@ -3519,10 +3972,13 @@
       <c r="E150" t="n">
         <v>13.82</v>
       </c>
-    </row>
-    <row r="151" spans="1:5">
+      <c r="F150" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B151" t="n">
         <v>100</v>
@@ -3536,10 +3992,13 @@
       <c r="E151" t="n">
         <v>17.81</v>
       </c>
-    </row>
-    <row r="152" spans="1:5">
+      <c r="F151" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B152" t="n">
         <v>100</v>
@@ -3553,10 +4012,13 @@
       <c r="E152" t="n">
         <v>19.33</v>
       </c>
-    </row>
-    <row r="153" spans="1:5">
+      <c r="F152" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B153" t="n">
         <v>100</v>
@@ -3570,10 +4032,13 @@
       <c r="E153" t="n">
         <v>23.59</v>
       </c>
-    </row>
-    <row r="154" spans="1:5">
+      <c r="F153" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B154" t="n">
         <v>100</v>
@@ -3587,10 +4052,13 @@
       <c r="E154" t="n">
         <v>30.66</v>
       </c>
-    </row>
-    <row r="155" spans="1:5">
+      <c r="F154" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B155" t="n">
         <v>100</v>
@@ -3604,10 +4072,13 @@
       <c r="E155" t="n">
         <v>10.6</v>
       </c>
-    </row>
-    <row r="156" spans="1:5">
+      <c r="F155" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B156" t="n">
         <v>100</v>
@@ -3621,10 +4092,13 @@
       <c r="E156" t="n">
         <v>12.89</v>
       </c>
-    </row>
-    <row r="157" spans="1:5">
+      <c r="F156" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B157" t="n">
         <v>100</v>
@@ -3638,10 +4112,13 @@
       <c r="E157" t="n">
         <v>17.39</v>
       </c>
-    </row>
-    <row r="158" spans="1:5">
+      <c r="F157" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B158" t="n">
         <v>100</v>
@@ -3655,10 +4132,13 @@
       <c r="E158" t="n">
         <v>27.61</v>
       </c>
-    </row>
-    <row r="159" spans="1:5">
+      <c r="F158" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B159" t="n">
         <v>100</v>
@@ -3672,10 +4152,13 @@
       <c r="E159" t="n">
         <v>31.73</v>
       </c>
-    </row>
-    <row r="160" spans="1:5">
+      <c r="F159" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B160" t="n">
         <v>100</v>
@@ -3689,10 +4172,13 @@
       <c r="E160" t="n">
         <v>41.35</v>
       </c>
-    </row>
-    <row r="161" spans="1:5">
+      <c r="F160" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B161" t="n">
         <v>100</v>
@@ -3706,10 +4192,13 @@
       <c r="E161" t="n">
         <v>16.62</v>
       </c>
-    </row>
-    <row r="162" spans="1:5">
+      <c r="F161" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B162" t="n">
         <v>100</v>
@@ -3723,10 +4212,13 @@
       <c r="E162" t="n">
         <v>20.16</v>
       </c>
-    </row>
-    <row r="163" spans="1:5">
+      <c r="F162" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B163" t="n">
         <v>100</v>
@@ -3740,10 +4232,13 @@
       <c r="E163" t="n">
         <v>26.59</v>
       </c>
-    </row>
-    <row r="164" spans="1:5">
+      <c r="F163" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B164" t="n">
         <v>100</v>
@@ -3757,10 +4252,13 @@
       <c r="E164" t="n">
         <v>28.36</v>
       </c>
-    </row>
-    <row r="165" spans="1:5">
+      <c r="F164" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B165" t="n">
         <v>100</v>
@@ -3774,10 +4272,13 @@
       <c r="E165" t="n">
         <v>33.71</v>
       </c>
-    </row>
-    <row r="166" spans="1:5">
+      <c r="F165" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B166" t="n">
         <v>100</v>
@@ -3791,10 +4292,13 @@
       <c r="E166" t="n">
         <v>43.45</v>
       </c>
-    </row>
-    <row r="167" spans="1:5">
+      <c r="F166" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B167" t="n">
         <v>100</v>
@@ -3808,10 +4312,13 @@
       <c r="E167" t="n">
         <v>16.53</v>
       </c>
-    </row>
-    <row r="168" spans="1:5">
+      <c r="F167" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B168" t="n">
         <v>100</v>
@@ -3825,10 +4332,13 @@
       <c r="E168" t="n">
         <v>20.46</v>
       </c>
-    </row>
-    <row r="169" spans="1:5">
+      <c r="F168" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B169" t="n">
         <v>100</v>
@@ -3842,10 +4352,13 @@
       <c r="E169" t="n">
         <v>27.58</v>
       </c>
-    </row>
-    <row r="170" spans="1:5">
+      <c r="F169" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B170" t="n">
         <v>100</v>
@@ -3859,10 +4372,13 @@
       <c r="E170" t="n">
         <v>7.85</v>
       </c>
-    </row>
-    <row r="171" spans="1:5">
+      <c r="F170" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B171" t="n">
         <v>100</v>
@@ -3876,10 +4392,13 @@
       <c r="E171" t="n">
         <v>9.86</v>
       </c>
-    </row>
-    <row r="172" spans="1:5">
+      <c r="F171" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B172" t="n">
         <v>100</v>
@@ -3893,10 +4412,13 @@
       <c r="E172" t="n">
         <v>13.2</v>
       </c>
-    </row>
-    <row r="173" spans="1:5">
+      <c r="F172" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B173" t="n">
         <v>100</v>
@@ -3910,10 +4432,13 @@
       <c r="E173" t="n">
         <v>4.82</v>
       </c>
-    </row>
-    <row r="174" spans="1:5">
+      <c r="F173" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B174" t="n">
         <v>100</v>
@@ -3927,10 +4452,13 @@
       <c r="E174" t="n">
         <v>5.42</v>
       </c>
-    </row>
-    <row r="175" spans="1:5">
+      <c r="F174" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B175" t="n">
         <v>100</v>
@@ -3944,10 +4472,13 @@
       <c r="E175" t="n">
         <v>6.64</v>
       </c>
-    </row>
-    <row r="176" spans="1:5">
+      <c r="F175" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B176" t="n">
         <v>100</v>
@@ -3961,10 +4492,13 @@
       <c r="E176" t="n">
         <v>12.05</v>
       </c>
-    </row>
-    <row r="177" spans="1:5">
+      <c r="F176" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B177" t="n">
         <v>100</v>
@@ -3978,10 +4512,13 @@
       <c r="E177" t="n">
         <v>14.59</v>
       </c>
-    </row>
-    <row r="178" spans="1:5">
+      <c r="F177" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B178" t="n">
         <v>100</v>
@@ -3995,10 +4532,13 @@
       <c r="E178" t="n">
         <v>19.45</v>
       </c>
-    </row>
-    <row r="179" spans="1:5">
+      <c r="F178" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B179" t="n">
         <v>100</v>
@@ -4012,10 +4552,13 @@
       <c r="E179" t="n">
         <v>6.65</v>
       </c>
-    </row>
-    <row r="180" spans="1:5">
+      <c r="F179" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B180" t="n">
         <v>100</v>
@@ -4029,10 +4572,13 @@
       <c r="E180" t="n">
         <v>7.84</v>
       </c>
-    </row>
-    <row r="181" spans="1:5">
+      <c r="F180" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B181" t="n">
         <v>100</v>
@@ -4046,10 +4592,13 @@
       <c r="E181" t="n">
         <v>10.03</v>
       </c>
-    </row>
-    <row r="182" spans="1:5">
+      <c r="F181" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B182" t="n">
         <v>100</v>
@@ -4063,10 +4612,13 @@
       <c r="E182" t="n">
         <v>1.62</v>
       </c>
-    </row>
-    <row r="183" spans="1:5">
+      <c r="F182" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B183" t="n">
         <v>100</v>
@@ -4080,10 +4632,13 @@
       <c r="E183" t="n">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="184" spans="1:5">
+      <c r="F183" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B184" t="n">
         <v>100</v>
@@ -4097,10 +4652,13 @@
       <c r="E184" t="n">
         <v>2.16</v>
       </c>
-    </row>
-    <row r="185" spans="1:5">
+      <c r="F184" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B185" t="n">
         <v>100</v>
@@ -4114,10 +4672,13 @@
       <c r="E185" t="n">
         <v>1.18</v>
       </c>
-    </row>
-    <row r="186" spans="1:5">
+      <c r="F185" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B186" t="n">
         <v>100</v>
@@ -4131,10 +4692,13 @@
       <c r="E186" t="n">
         <v>1.24</v>
       </c>
-    </row>
-    <row r="187" spans="1:5">
+      <c r="F186" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B187" t="n">
         <v>100</v>
@@ -4148,10 +4712,13 @@
       <c r="E187" t="n">
         <v>1.38</v>
       </c>
-    </row>
-    <row r="188" spans="1:5">
+      <c r="F187" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B188" t="n">
         <v>100</v>
@@ -4165,10 +4732,13 @@
       <c r="E188" t="n">
         <v>2.24</v>
       </c>
-    </row>
-    <row r="189" spans="1:5">
+      <c r="F188" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B189" t="n">
         <v>100</v>
@@ -4182,10 +4752,13 @@
       <c r="E189" t="n">
         <v>2.59</v>
       </c>
-    </row>
-    <row r="190" spans="1:5">
+      <c r="F189" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B190" t="n">
         <v>100</v>
@@ -4199,10 +4772,13 @@
       <c r="E190" t="n">
         <v>3.31</v>
       </c>
-    </row>
-    <row r="191" spans="1:5">
+      <c r="F190" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B191" t="n">
         <v>100</v>
@@ -4216,10 +4792,13 @@
       <c r="E191" t="n">
         <v>1.46</v>
       </c>
-    </row>
-    <row r="192" spans="1:5">
+      <c r="F191" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B192" t="n">
         <v>100</v>
@@ -4233,10 +4812,13 @@
       <c r="E192" t="n">
         <v>1.58</v>
       </c>
-    </row>
-    <row r="193" spans="1:5">
+      <c r="F192" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B193" t="n">
         <v>100</v>
@@ -4249,6 +4831,9 @@
       </c>
       <c r="E193" t="n">
         <v>1.86</v>
+      </c>
+      <c r="F193" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
